--- a/HR_Data_Analysis_Project.xlsx
+++ b/HR_Data_Analysis_Project.xlsx
@@ -5,12 +5,12 @@
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rahul Chavan\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rahul Chavan\Desktop\HR Analytics Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB43F7E7-5320-4D77-B8B1-A550DE8DBBE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7B87FD-8E95-457B-8EB8-F82F4C95AC76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{6624E436-E7CB-403D-932E-F5A91BCD8244}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{6624E436-E7CB-403D-932E-F5A91BCD8244}"/>
   </bookViews>
   <sheets>
     <sheet name="HR DATA" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId4"/>
+    <pivotCache cacheId="91" r:id="rId4"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -792,12 +792,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -807,34 +817,789 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="272">
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="bottom"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment vertical="center"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="right"/>
+    </dxf>
     <dxf>
       <alignment horizontal="right"/>
     </dxf>
@@ -913,7 +1678,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[HR_DB PROJECT.xlsx]DASHBOARD!PivotTable3</c:name>
+    <c:name>[HR_Data_Analysis_Project.xlsx.xlsx]DASHBOARD!PivotTable3</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -1380,7 +2145,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[HR_DB PROJECT.xlsx]DASHBOARD!PivotTable1</c:name>
+    <c:name>[HR_Data_Analysis_Project.xlsx.xlsx]DASHBOARD!PivotTable1</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -1975,7 +2740,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[HR_DB PROJECT.xlsx]DASHBOARD!PivotTable2</c:name>
+    <c:name>[HR_Data_Analysis_Project.xlsx.xlsx]DASHBOARD!PivotTable2</c:name>
     <c:fmtId val="0"/>
   </c:pivotSource>
   <c:chart>
@@ -2161,7 +2926,7 @@
                   <c:v>1170000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1909000</c:v>
+                  <c:v>1914000</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>1397000</c:v>
@@ -4099,15 +4864,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1569720</xdr:colOff>
+      <xdr:colOff>1501140</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>64770</xdr:rowOff>
+      <xdr:rowOff>80010</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>922020</xdr:colOff>
+      <xdr:colOff>807720</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>26670</xdr:rowOff>
+      <xdr:rowOff>41910</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4140,8 +4905,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1744980" cy="1592580"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="6" name="DEPARTMENT">
@@ -4164,7 +4929,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -4213,8 +4978,8 @@
       <xdr:rowOff>15241</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1760220" cy="1432560"/>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="7" name="SALARY">
@@ -4237,7 +5002,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -4282,215 +5047,16 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Rahul Chavan" refreshedDate="46134.935430439815" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="100" xr:uid="{C49B238D-1150-461D-8FFE-51FE4BB95872}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Rahul Chavan" refreshedDate="46138.476065972223" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="100" xr:uid="{C49B238D-1150-461D-8FFE-51FE4BB95872}">
   <cacheSource type="worksheet">
     <worksheetSource ref="A1:I101" sheet="HR DATA"/>
   </cacheSource>
   <cacheFields count="12">
     <cacheField name="EMP_ID" numFmtId="0">
-      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="100" count="100">
-        <n v="1"/>
-        <n v="2"/>
-        <n v="3"/>
-        <n v="4"/>
-        <n v="5"/>
-        <n v="6"/>
-        <n v="7"/>
-        <n v="8"/>
-        <n v="9"/>
-        <n v="10"/>
-        <n v="11"/>
-        <n v="12"/>
-        <n v="13"/>
-        <n v="14"/>
-        <n v="15"/>
-        <n v="16"/>
-        <n v="17"/>
-        <n v="18"/>
-        <n v="19"/>
-        <n v="20"/>
-        <n v="21"/>
-        <n v="22"/>
-        <n v="23"/>
-        <n v="24"/>
-        <n v="25"/>
-        <n v="26"/>
-        <n v="27"/>
-        <n v="28"/>
-        <n v="29"/>
-        <n v="30"/>
-        <n v="31"/>
-        <n v="32"/>
-        <n v="33"/>
-        <n v="34"/>
-        <n v="35"/>
-        <n v="36"/>
-        <n v="37"/>
-        <n v="38"/>
-        <n v="39"/>
-        <n v="40"/>
-        <n v="41"/>
-        <n v="42"/>
-        <n v="43"/>
-        <n v="44"/>
-        <n v="45"/>
-        <n v="46"/>
-        <n v="47"/>
-        <n v="48"/>
-        <n v="49"/>
-        <n v="50"/>
-        <n v="51"/>
-        <n v="52"/>
-        <n v="53"/>
-        <n v="54"/>
-        <n v="55"/>
-        <n v="56"/>
-        <n v="57"/>
-        <n v="58"/>
-        <n v="59"/>
-        <n v="60"/>
-        <n v="61"/>
-        <n v="62"/>
-        <n v="63"/>
-        <n v="64"/>
-        <n v="65"/>
-        <n v="66"/>
-        <n v="67"/>
-        <n v="68"/>
-        <n v="69"/>
-        <n v="70"/>
-        <n v="71"/>
-        <n v="72"/>
-        <n v="73"/>
-        <n v="74"/>
-        <n v="75"/>
-        <n v="76"/>
-        <n v="77"/>
-        <n v="78"/>
-        <n v="79"/>
-        <n v="80"/>
-        <n v="81"/>
-        <n v="82"/>
-        <n v="83"/>
-        <n v="84"/>
-        <n v="85"/>
-        <n v="86"/>
-        <n v="87"/>
-        <n v="88"/>
-        <n v="89"/>
-        <n v="90"/>
-        <n v="91"/>
-        <n v="92"/>
-        <n v="93"/>
-        <n v="94"/>
-        <n v="95"/>
-        <n v="96"/>
-        <n v="97"/>
-        <n v="98"/>
-        <n v="99"/>
-        <n v="100"/>
-      </sharedItems>
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="100"/>
     </cacheField>
     <cacheField name="NAME" numFmtId="0">
-      <sharedItems count="97">
-        <s v="Rahul"/>
-        <s v="Sneha"/>
-        <s v="Amit"/>
-        <s v="Priya"/>
-        <s v="Rohit"/>
-        <s v="Neha"/>
-        <s v="Arjun"/>
-        <s v="Kavita"/>
-        <s v="Suresh"/>
-        <s v="Pooja"/>
-        <s v="Karan"/>
-        <s v="Meena"/>
-        <s v="Vijay"/>
-        <s v="Anjali"/>
-        <s v="Deepak"/>
-        <s v="Ramesh"/>
-        <s v="Komal"/>
-        <s v="Nitin"/>
-        <s v="Seema"/>
-        <s v="Varun"/>
-        <s v="Ritika"/>
-        <s v="Manish"/>
-        <s v="Alok"/>
-        <s v="Shweta"/>
-        <s v="Tarun"/>
-        <s v="Nisha"/>
-        <s v="Gaurav"/>
-        <s v="Payal"/>
-        <s v="Akash"/>
-        <s v="Divya"/>
-        <s v="Ayesha"/>
-        <s v="Ravi"/>
-        <s v="Sunil"/>
-        <s v="Pallavi"/>
-        <s v="Harsh"/>
-        <s v="Kiran"/>
-        <s v="Neelam"/>
-        <s v="Yogesh"/>
-        <s v="Tanvi"/>
-        <s v="Sameer"/>
-        <s v="Pankaj"/>
-        <s v="Rekha"/>
-        <s v="Mohit"/>
-        <s v="Isha"/>
-        <s v="Naveen"/>
-        <s v="Ritu"/>
-        <s v="Vikas"/>
-        <s v="Sonal"/>
-        <s v="Ajay"/>
-        <s v="Deepa"/>
-        <s v="Rohan"/>
-        <s v="Simran"/>
-        <s v="Kunal"/>
-        <s v="Mehul"/>
-        <s v="Nikita"/>
-        <s v="Sanjay"/>
-        <s v="Alisha"/>
-        <s v="Girish"/>
-        <s v="Ankit"/>
-        <s v="Preeti"/>
-        <s v="Aman"/>
-        <s v="Rachna"/>
-        <s v="Vivek"/>
-        <s v="Keshav"/>
-        <s v="Sangeeta"/>
-        <s v="Nilesh"/>
-        <s v="Tina"/>
-        <s v="Abhishek"/>
-        <s v="Bhavna"/>
-        <s v="Kapil"/>
-        <s v="Juhi"/>
-        <s v="Dinesh"/>
-        <s v="Shilpa"/>
-        <s v="Rajat"/>
-        <s v="Monika"/>
-        <s v="Arvind"/>
-        <s v="Swati"/>
-        <s v="Lokesh"/>
-        <s v="Neetu"/>
-        <s v="Varsha"/>
-        <s v="Prakash"/>
-        <s v="Ritesh"/>
-        <s v="Anu"/>
-        <s v="Gopal"/>
-        <s v="Suman"/>
-        <s v="Imran"/>
-        <s v="Kritika"/>
-        <s v="Ashok"/>
-        <s v="Reena"/>
-        <s v="Manoj"/>
-        <s v="Ruchi"/>
-        <s v="Dev"/>
-        <s v="Kajal"/>
-        <s v="Siddharth"/>
-        <s v="Priti"/>
-        <s v="Geeta"/>
-        <s v="Akshay"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="DEPARTMENT" numFmtId="0">
       <sharedItems count="4">
@@ -4501,35 +5067,11 @@
       </sharedItems>
     </cacheField>
     <cacheField name="DESIGNATION" numFmtId="0">
-      <sharedItems count="23">
-        <s v="Developer"/>
-        <s v="Recruiter"/>
-        <s v="Senior Developer"/>
-        <s v="Accountant"/>
-        <s v="Sales Executive"/>
-        <s v="HR Manager"/>
-        <s v="Team Lead"/>
-        <s v="Analyst"/>
-        <s v="Manager"/>
-        <s v="Tester"/>
-        <s v="Senior Analyst"/>
-        <s v="Executive"/>
-        <s v="Support Engineer"/>
-        <s v="Coordinator"/>
-        <s v="Architect"/>
-        <s v="DevOps Engineer"/>
-        <s v="HR Executive"/>
-        <s v="Data Analyst"/>
-        <s v="Data Scientist"/>
-        <s v="Backend Developer"/>
-        <s v="Frontend Developer"/>
-        <s v="Data Engineer"/>
-        <s v="System Admin"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="SALARY" numFmtId="0">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="39000" maxValue="95000" count="48">
-        <n v="55000"/>
+        <n v="60000"/>
         <n v="42000"/>
         <n v="75000"/>
         <n v="48000"/>
@@ -4542,7 +5084,6 @@
         <n v="68000"/>
         <n v="40000"/>
         <n v="47000"/>
-        <n v="60000"/>
         <n v="80000"/>
         <n v="39000"/>
         <n v="95000"/>
@@ -4560,6 +5101,7 @@
         <n v="53000"/>
         <n v="62000"/>
         <n v="51000"/>
+        <n v="55000"/>
         <n v="77000"/>
         <n v="85000"/>
         <n v="56000"/>
@@ -4580,14 +5122,7 @@
       </sharedItems>
     </cacheField>
     <cacheField name="CITY" numFmtId="0">
-      <sharedItems count="6">
-        <s v="Mumbai"/>
-        <s v="Pune"/>
-        <s v="Bangalore"/>
-        <s v="Delhi"/>
-        <s v="Hyderabad"/>
-        <s v="Chennai"/>
-      </sharedItems>
+      <sharedItems/>
     </cacheField>
     <cacheField name="JOIN_DATE" numFmtId="14">
       <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2016-11-11T00:00:00" maxDate="2022-09-10T00:00:00" count="74">
@@ -4739,1101 +5274,1101 @@
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="100">
   <r>
+    <n v="1"/>
+    <s v="Rahul"/>
     <x v="0"/>
+    <s v="Developer"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="Mumbai"/>
     <x v="0"/>
     <n v="3"/>
     <x v="0"/>
   </r>
   <r>
+    <n v="2"/>
+    <s v="Sneha"/>
     <x v="1"/>
+    <s v="Recruiter"/>
     <x v="1"/>
-    <x v="1"/>
-    <x v="1"/>
-    <x v="1"/>
-    <x v="1"/>
+    <s v="Pune"/>
     <x v="1"/>
     <n v="4"/>
     <x v="1"/>
   </r>
   <r>
+    <n v="3"/>
+    <s v="Amit"/>
+    <x v="0"/>
+    <s v="Senior Developer"/>
     <x v="2"/>
-    <x v="2"/>
-    <x v="0"/>
-    <x v="2"/>
-    <x v="2"/>
-    <x v="2"/>
+    <s v="Bangalore"/>
     <x v="2"/>
     <n v="6"/>
     <x v="0"/>
   </r>
   <r>
+    <n v="4"/>
+    <s v="Priya"/>
+    <x v="2"/>
+    <s v="Accountant"/>
     <x v="3"/>
-    <x v="3"/>
-    <x v="2"/>
-    <x v="3"/>
-    <x v="3"/>
-    <x v="3"/>
+    <s v="Delhi"/>
     <x v="3"/>
     <n v="2"/>
     <x v="1"/>
   </r>
   <r>
+    <n v="5"/>
+    <s v="Rohit"/>
+    <x v="3"/>
+    <s v="Sales Executive"/>
     <x v="4"/>
-    <x v="4"/>
-    <x v="3"/>
-    <x v="4"/>
-    <x v="4"/>
-    <x v="0"/>
+    <s v="Mumbai"/>
     <x v="4"/>
     <n v="3"/>
     <x v="0"/>
   </r>
   <r>
+    <n v="6"/>
+    <s v="Neha"/>
+    <x v="1"/>
+    <s v="HR Manager"/>
     <x v="5"/>
-    <x v="5"/>
-    <x v="1"/>
-    <x v="5"/>
-    <x v="5"/>
-    <x v="1"/>
+    <s v="Pune"/>
     <x v="5"/>
     <n v="7"/>
     <x v="1"/>
   </r>
   <r>
+    <n v="7"/>
+    <s v="Arjun"/>
+    <x v="0"/>
+    <s v="Team Lead"/>
     <x v="6"/>
-    <x v="6"/>
-    <x v="0"/>
-    <x v="6"/>
-    <x v="6"/>
-    <x v="4"/>
+    <s v="Hyderabad"/>
     <x v="6"/>
     <n v="8"/>
     <x v="0"/>
   </r>
   <r>
+    <n v="8"/>
+    <s v="Kavita"/>
+    <x v="2"/>
+    <s v="Analyst"/>
     <x v="7"/>
-    <x v="7"/>
-    <x v="2"/>
-    <x v="7"/>
-    <x v="7"/>
-    <x v="3"/>
+    <s v="Delhi"/>
     <x v="7"/>
     <n v="4"/>
     <x v="1"/>
   </r>
   <r>
+    <n v="9"/>
+    <s v="Suresh"/>
+    <x v="3"/>
+    <s v="Manager"/>
     <x v="8"/>
-    <x v="8"/>
-    <x v="3"/>
-    <x v="8"/>
-    <x v="8"/>
-    <x v="5"/>
+    <s v="Chennai"/>
     <x v="8"/>
     <n v="5"/>
     <x v="0"/>
   </r>
   <r>
+    <n v="10"/>
+    <s v="Pooja"/>
+    <x v="0"/>
+    <s v="Tester"/>
     <x v="9"/>
-    <x v="9"/>
-    <x v="0"/>
-    <x v="9"/>
-    <x v="9"/>
-    <x v="0"/>
+    <s v="Mumbai"/>
     <x v="9"/>
     <n v="2"/>
     <x v="1"/>
   </r>
   <r>
+    <n v="11"/>
+    <s v="Karan"/>
+    <x v="2"/>
+    <s v="Senior Analyst"/>
     <x v="10"/>
-    <x v="10"/>
-    <x v="2"/>
-    <x v="10"/>
-    <x v="10"/>
-    <x v="2"/>
+    <s v="Bangalore"/>
     <x v="10"/>
     <n v="6"/>
     <x v="0"/>
   </r>
   <r>
+    <n v="12"/>
+    <s v="Meena"/>
+    <x v="1"/>
+    <s v="Executive"/>
     <x v="11"/>
-    <x v="11"/>
-    <x v="1"/>
-    <x v="11"/>
-    <x v="11"/>
-    <x v="3"/>
+    <s v="Delhi"/>
     <x v="11"/>
     <n v="3"/>
     <x v="1"/>
   </r>
   <r>
+    <n v="13"/>
+    <s v="Vijay"/>
+    <x v="3"/>
+    <s v="Executive"/>
     <x v="12"/>
-    <x v="12"/>
-    <x v="3"/>
-    <x v="11"/>
-    <x v="12"/>
-    <x v="1"/>
+    <s v="Pune"/>
     <x v="12"/>
     <n v="2"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="13"/>
-    <x v="13"/>
+    <n v="14"/>
+    <s v="Anjali"/>
     <x v="0"/>
+    <s v="Developer"/>
     <x v="0"/>
-    <x v="13"/>
-    <x v="4"/>
+    <s v="Hyderabad"/>
     <x v="13"/>
     <n v="5"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="14"/>
-    <x v="14"/>
+    <n v="15"/>
+    <s v="Deepak"/>
     <x v="2"/>
-    <x v="8"/>
-    <x v="14"/>
-    <x v="0"/>
+    <s v="Manager"/>
+    <x v="13"/>
+    <s v="Mumbai"/>
     <x v="14"/>
     <n v="7"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="15"/>
-    <x v="15"/>
+    <n v="16"/>
+    <s v="Ramesh"/>
     <x v="0"/>
-    <x v="12"/>
+    <s v="Support Engineer"/>
     <x v="3"/>
-    <x v="5"/>
+    <s v="Chennai"/>
     <x v="15"/>
     <n v="3"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="16"/>
-    <x v="16"/>
+    <n v="17"/>
+    <s v="Komal"/>
     <x v="1"/>
-    <x v="13"/>
-    <x v="15"/>
-    <x v="2"/>
+    <s v="Coordinator"/>
+    <x v="14"/>
+    <s v="Bangalore"/>
     <x v="16"/>
     <n v="2"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="17"/>
-    <x v="17"/>
+    <n v="18"/>
+    <s v="Nitin"/>
     <x v="3"/>
-    <x v="4"/>
+    <s v="Sales Executive"/>
     <x v="7"/>
-    <x v="3"/>
+    <s v="Delhi"/>
     <x v="17"/>
     <n v="4"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="18"/>
-    <x v="18"/>
+    <n v="19"/>
+    <s v="Seema"/>
     <x v="0"/>
-    <x v="14"/>
-    <x v="16"/>
-    <x v="4"/>
+    <s v="Architect"/>
+    <x v="15"/>
+    <s v="Hyderabad"/>
     <x v="18"/>
     <n v="9"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="19"/>
-    <x v="19"/>
+    <n v="20"/>
+    <s v="Varun"/>
     <x v="2"/>
-    <x v="3"/>
-    <x v="17"/>
-    <x v="1"/>
+    <s v="Accountant"/>
+    <x v="16"/>
+    <s v="Pune"/>
     <x v="19"/>
     <n v="3"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="20"/>
-    <x v="20"/>
+    <n v="21"/>
+    <s v="Ritika"/>
     <x v="1"/>
-    <x v="1"/>
-    <x v="18"/>
-    <x v="0"/>
+    <s v="Recruiter"/>
+    <x v="17"/>
+    <s v="Mumbai"/>
     <x v="20"/>
     <n v="3"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="21"/>
-    <x v="21"/>
+    <n v="22"/>
+    <s v="Manish"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="19"/>
-    <x v="2"/>
+    <s v="Developer"/>
+    <x v="18"/>
+    <s v="Bangalore"/>
     <x v="21"/>
     <n v="5"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="22"/>
-    <x v="22"/>
+    <n v="23"/>
+    <s v="Alok"/>
     <x v="3"/>
-    <x v="8"/>
-    <x v="20"/>
-    <x v="4"/>
+    <s v="Manager"/>
+    <x v="19"/>
+    <s v="Hyderabad"/>
     <x v="22"/>
     <n v="6"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="23"/>
-    <x v="23"/>
+    <n v="24"/>
+    <s v="Shweta"/>
     <x v="2"/>
-    <x v="7"/>
-    <x v="21"/>
-    <x v="3"/>
+    <s v="Analyst"/>
+    <x v="20"/>
+    <s v="Delhi"/>
     <x v="23"/>
     <n v="3"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="24"/>
-    <x v="24"/>
+    <n v="25"/>
+    <s v="Tarun"/>
     <x v="0"/>
-    <x v="15"/>
-    <x v="22"/>
-    <x v="5"/>
+    <s v="DevOps Engineer"/>
+    <x v="21"/>
+    <s v="Chennai"/>
     <x v="24"/>
     <n v="7"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="25"/>
-    <x v="25"/>
+    <n v="26"/>
+    <s v="Nisha"/>
     <x v="1"/>
-    <x v="16"/>
-    <x v="23"/>
-    <x v="1"/>
+    <s v="HR Executive"/>
+    <x v="22"/>
+    <s v="Pune"/>
     <x v="25"/>
     <n v="2"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="26"/>
-    <x v="26"/>
+    <n v="27"/>
+    <s v="Gaurav"/>
     <x v="3"/>
-    <x v="11"/>
-    <x v="24"/>
-    <x v="0"/>
+    <s v="Executive"/>
+    <x v="23"/>
+    <s v="Mumbai"/>
     <x v="26"/>
     <n v="3"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="27"/>
-    <x v="27"/>
+    <n v="28"/>
+    <s v="Payal"/>
     <x v="2"/>
-    <x v="3"/>
+    <s v="Accountant"/>
     <x v="12"/>
-    <x v="2"/>
+    <s v="Bangalore"/>
     <x v="27"/>
     <n v="4"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="28"/>
-    <x v="28"/>
+    <n v="29"/>
+    <s v="Akash"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="25"/>
-    <x v="3"/>
+    <s v="Developer"/>
+    <x v="24"/>
+    <s v="Delhi"/>
     <x v="28"/>
     <n v="6"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="29"/>
-    <x v="29"/>
+    <n v="30"/>
+    <s v="Divya"/>
     <x v="1"/>
+    <s v="Manager"/>
     <x v="8"/>
-    <x v="8"/>
-    <x v="4"/>
+    <s v="Hyderabad"/>
     <x v="29"/>
     <n v="7"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="30"/>
-    <x v="30"/>
+    <n v="31"/>
+    <s v="Ayesha"/>
     <x v="0"/>
-    <x v="17"/>
+    <s v="Data Analyst"/>
     <x v="5"/>
-    <x v="0"/>
+    <s v="Mumbai"/>
     <x v="30"/>
     <n v="5"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="31"/>
-    <x v="31"/>
+    <n v="32"/>
+    <s v="Ravi"/>
     <x v="3"/>
-    <x v="11"/>
+    <s v="Executive"/>
     <x v="3"/>
-    <x v="1"/>
+    <s v="Pune"/>
     <x v="31"/>
     <n v="3"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="32"/>
-    <x v="32"/>
+    <n v="33"/>
+    <s v="Sunil"/>
     <x v="2"/>
-    <x v="8"/>
-    <x v="26"/>
-    <x v="3"/>
+    <s v="Manager"/>
+    <x v="25"/>
+    <s v="Delhi"/>
     <x v="32"/>
     <n v="7"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="33"/>
-    <x v="33"/>
+    <n v="34"/>
+    <s v="Pallavi"/>
     <x v="1"/>
+    <s v="Recruiter"/>
     <x v="1"/>
-    <x v="1"/>
-    <x v="2"/>
+    <s v="Bangalore"/>
     <x v="33"/>
     <n v="2"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="34"/>
-    <x v="34"/>
+    <n v="35"/>
+    <s v="Harsh"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="27"/>
-    <x v="4"/>
+    <s v="Developer"/>
+    <x v="26"/>
+    <s v="Hyderabad"/>
     <x v="34"/>
     <n v="4"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="35"/>
-    <x v="35"/>
+    <n v="36"/>
+    <s v="Kiran"/>
     <x v="3"/>
-    <x v="8"/>
+    <s v="Manager"/>
     <x v="2"/>
-    <x v="5"/>
+    <s v="Chennai"/>
     <x v="35"/>
     <n v="6"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="36"/>
-    <x v="36"/>
+    <n v="37"/>
+    <s v="Neelam"/>
     <x v="2"/>
-    <x v="7"/>
-    <x v="28"/>
-    <x v="0"/>
+    <s v="Analyst"/>
+    <x v="27"/>
+    <s v="Mumbai"/>
     <x v="36"/>
     <n v="4"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="37"/>
-    <x v="37"/>
+    <n v="38"/>
+    <s v="Yogesh"/>
     <x v="0"/>
-    <x v="9"/>
-    <x v="17"/>
-    <x v="3"/>
+    <s v="Tester"/>
+    <x v="16"/>
+    <s v="Delhi"/>
     <x v="37"/>
     <n v="2"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="38"/>
-    <x v="38"/>
+    <n v="39"/>
+    <s v="Tanvi"/>
     <x v="1"/>
-    <x v="13"/>
+    <s v="Coordinator"/>
     <x v="11"/>
-    <x v="1"/>
+    <s v="Pune"/>
     <x v="4"/>
     <n v="3"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="39"/>
-    <x v="39"/>
+    <n v="40"/>
+    <s v="Sameer"/>
     <x v="3"/>
-    <x v="11"/>
+    <s v="Executive"/>
     <x v="4"/>
-    <x v="2"/>
+    <s v="Bangalore"/>
     <x v="38"/>
     <n v="5"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="40"/>
-    <x v="40"/>
+    <n v="41"/>
+    <s v="Pankaj"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="29"/>
-    <x v="5"/>
+    <s v="Developer"/>
+    <x v="28"/>
+    <s v="Chennai"/>
     <x v="39"/>
     <n v="6"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="41"/>
-    <x v="41"/>
+    <n v="42"/>
+    <s v="Rekha"/>
     <x v="2"/>
+    <s v="Accountant"/>
     <x v="3"/>
-    <x v="3"/>
-    <x v="4"/>
+    <s v="Hyderabad"/>
     <x v="40"/>
     <n v="3"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="42"/>
-    <x v="42"/>
+    <n v="43"/>
+    <s v="Mohit"/>
     <x v="3"/>
-    <x v="11"/>
-    <x v="30"/>
-    <x v="3"/>
+    <s v="Executive"/>
+    <x v="29"/>
+    <s v="Delhi"/>
     <x v="41"/>
     <n v="4"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="43"/>
-    <x v="43"/>
+    <n v="44"/>
+    <s v="Isha"/>
     <x v="1"/>
-    <x v="8"/>
-    <x v="20"/>
-    <x v="0"/>
+    <s v="Manager"/>
+    <x v="19"/>
+    <s v="Mumbai"/>
     <x v="42"/>
     <n v="7"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="44"/>
-    <x v="44"/>
+    <n v="45"/>
+    <s v="Naveen"/>
     <x v="0"/>
-    <x v="15"/>
-    <x v="14"/>
-    <x v="1"/>
+    <s v="DevOps Engineer"/>
+    <x v="13"/>
+    <s v="Pune"/>
     <x v="43"/>
     <n v="6"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="45"/>
-    <x v="45"/>
+    <n v="46"/>
+    <s v="Ritu"/>
     <x v="2"/>
-    <x v="7"/>
-    <x v="0"/>
-    <x v="2"/>
+    <s v="Analyst"/>
+    <x v="30"/>
+    <s v="Bangalore"/>
     <x v="44"/>
     <n v="5"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="46"/>
-    <x v="46"/>
+    <n v="47"/>
+    <s v="Vikas"/>
     <x v="3"/>
-    <x v="8"/>
+    <s v="Manager"/>
     <x v="31"/>
-    <x v="4"/>
+    <s v="Hyderabad"/>
     <x v="45"/>
     <n v="7"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="47"/>
-    <x v="47"/>
+    <n v="48"/>
+    <s v="Sonal"/>
     <x v="1"/>
-    <x v="11"/>
-    <x v="23"/>
-    <x v="3"/>
+    <s v="Executive"/>
+    <x v="22"/>
+    <s v="Delhi"/>
     <x v="46"/>
     <n v="2"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="48"/>
-    <x v="48"/>
+    <n v="49"/>
+    <s v="Ajay"/>
     <x v="0"/>
-    <x v="12"/>
-    <x v="24"/>
-    <x v="0"/>
+    <s v="Support Engineer"/>
+    <x v="23"/>
+    <s v="Mumbai"/>
     <x v="19"/>
     <n v="3"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="49"/>
-    <x v="49"/>
+    <n v="50"/>
+    <s v="Deepa"/>
     <x v="2"/>
-    <x v="3"/>
+    <s v="Accountant"/>
     <x v="12"/>
-    <x v="5"/>
+    <s v="Chennai"/>
     <x v="15"/>
     <n v="3"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="50"/>
-    <x v="50"/>
+    <n v="51"/>
+    <s v="Rohan"/>
     <x v="0"/>
+    <s v="Developer"/>
     <x v="0"/>
-    <x v="13"/>
-    <x v="2"/>
+    <s v="Bangalore"/>
     <x v="47"/>
     <n v="5"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="51"/>
-    <x v="51"/>
+    <n v="52"/>
+    <s v="Simran"/>
     <x v="1"/>
-    <x v="1"/>
-    <x v="18"/>
-    <x v="4"/>
+    <s v="Recruiter"/>
+    <x v="17"/>
+    <s v="Hyderabad"/>
     <x v="23"/>
     <n v="3"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="52"/>
-    <x v="52"/>
+    <n v="53"/>
+    <s v="Kunal"/>
     <x v="3"/>
-    <x v="11"/>
+    <s v="Executive"/>
     <x v="7"/>
-    <x v="0"/>
+    <s v="Mumbai"/>
     <x v="48"/>
     <n v="4"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="53"/>
-    <x v="53"/>
+    <n v="54"/>
+    <s v="Mehul"/>
     <x v="2"/>
-    <x v="8"/>
+    <s v="Manager"/>
     <x v="32"/>
-    <x v="1"/>
+    <s v="Pune"/>
     <x v="49"/>
     <n v="8"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="54"/>
-    <x v="54"/>
+    <n v="55"/>
+    <s v="Nikita"/>
     <x v="0"/>
-    <x v="18"/>
+    <s v="Data Scientist"/>
     <x v="6"/>
-    <x v="3"/>
+    <s v="Delhi"/>
     <x v="50"/>
     <n v="6"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="55"/>
-    <x v="55"/>
+    <n v="56"/>
+    <s v="Sanjay"/>
     <x v="3"/>
-    <x v="8"/>
-    <x v="22"/>
-    <x v="2"/>
+    <s v="Manager"/>
+    <x v="21"/>
+    <s v="Bangalore"/>
     <x v="51"/>
     <n v="7"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="56"/>
-    <x v="56"/>
+    <n v="57"/>
+    <s v="Alisha"/>
     <x v="1"/>
-    <x v="13"/>
-    <x v="15"/>
-    <x v="5"/>
+    <s v="Coordinator"/>
+    <x v="14"/>
+    <s v="Chennai"/>
     <x v="52"/>
     <n v="2"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="57"/>
-    <x v="57"/>
+    <n v="58"/>
+    <s v="Girish"/>
     <x v="2"/>
-    <x v="7"/>
+    <s v="Analyst"/>
     <x v="33"/>
-    <x v="0"/>
+    <s v="Mumbai"/>
     <x v="21"/>
     <n v="5"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="58"/>
-    <x v="58"/>
+    <n v="59"/>
+    <s v="Ankit"/>
     <x v="0"/>
-    <x v="0"/>
+    <s v="Developer"/>
     <x v="34"/>
-    <x v="4"/>
+    <s v="Hyderabad"/>
     <x v="53"/>
     <n v="6"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="59"/>
-    <x v="59"/>
+    <n v="60"/>
+    <s v="Preeti"/>
     <x v="1"/>
-    <x v="8"/>
+    <s v="Manager"/>
     <x v="35"/>
-    <x v="1"/>
+    <s v="Pune"/>
     <x v="54"/>
     <n v="7"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="60"/>
-    <x v="60"/>
+    <n v="61"/>
+    <s v="Aman"/>
     <x v="0"/>
-    <x v="19"/>
+    <s v="Backend Developer"/>
     <x v="36"/>
-    <x v="0"/>
+    <s v="Mumbai"/>
     <x v="55"/>
     <n v="5"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="61"/>
-    <x v="61"/>
+    <n v="62"/>
+    <s v="Rachna"/>
     <x v="1"/>
-    <x v="1"/>
+    <s v="Recruiter"/>
     <x v="37"/>
-    <x v="3"/>
+    <s v="Delhi"/>
     <x v="56"/>
     <n v="3"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="62"/>
-    <x v="62"/>
+    <n v="63"/>
+    <s v="Vivek"/>
     <x v="2"/>
-    <x v="7"/>
-    <x v="27"/>
-    <x v="1"/>
+    <s v="Analyst"/>
+    <x v="26"/>
+    <s v="Pune"/>
     <x v="57"/>
     <n v="4"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="63"/>
-    <x v="9"/>
+    <n v="64"/>
+    <s v="Pooja"/>
     <x v="3"/>
-    <x v="11"/>
-    <x v="30"/>
-    <x v="2"/>
+    <s v="Executive"/>
+    <x v="29"/>
+    <s v="Bangalore"/>
     <x v="19"/>
     <n v="3"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="64"/>
-    <x v="63"/>
+    <n v="65"/>
+    <s v="Keshav"/>
     <x v="0"/>
-    <x v="20"/>
-    <x v="13"/>
-    <x v="4"/>
+    <s v="Frontend Developer"/>
+    <x v="0"/>
+    <s v="Hyderabad"/>
     <x v="22"/>
     <n v="6"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="65"/>
-    <x v="64"/>
+    <n v="66"/>
+    <s v="Sangeeta"/>
     <x v="2"/>
-    <x v="8"/>
+    <s v="Manager"/>
     <x v="38"/>
-    <x v="5"/>
+    <s v="Chennai"/>
     <x v="45"/>
     <n v="7"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="66"/>
-    <x v="65"/>
+    <n v="67"/>
+    <s v="Nilesh"/>
     <x v="3"/>
-    <x v="8"/>
+    <s v="Manager"/>
     <x v="39"/>
-    <x v="0"/>
+    <s v="Mumbai"/>
     <x v="39"/>
     <n v="6"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="67"/>
-    <x v="66"/>
+    <n v="68"/>
+    <s v="Tina"/>
     <x v="1"/>
-    <x v="13"/>
+    <s v="Coordinator"/>
     <x v="11"/>
-    <x v="1"/>
+    <s v="Pune"/>
     <x v="58"/>
     <n v="2"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="68"/>
-    <x v="67"/>
+    <n v="69"/>
+    <s v="Abhishek"/>
     <x v="0"/>
-    <x v="21"/>
-    <x v="26"/>
-    <x v="3"/>
+    <s v="Data Engineer"/>
+    <x v="25"/>
+    <s v="Delhi"/>
     <x v="42"/>
     <n v="7"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="69"/>
-    <x v="68"/>
+    <n v="70"/>
+    <s v="Bhavna"/>
     <x v="2"/>
+    <s v="Accountant"/>
     <x v="3"/>
-    <x v="3"/>
-    <x v="2"/>
+    <s v="Bangalore"/>
     <x v="4"/>
     <n v="3"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="70"/>
-    <x v="69"/>
+    <n v="71"/>
+    <s v="Kapil"/>
     <x v="3"/>
-    <x v="11"/>
+    <s v="Executive"/>
     <x v="4"/>
-    <x v="4"/>
+    <s v="Hyderabad"/>
     <x v="59"/>
     <n v="4"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="71"/>
-    <x v="70"/>
+    <n v="72"/>
+    <s v="Juhi"/>
     <x v="1"/>
-    <x v="11"/>
+    <s v="Executive"/>
     <x v="1"/>
-    <x v="5"/>
+    <s v="Chennai"/>
     <x v="60"/>
     <n v="3"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="72"/>
-    <x v="71"/>
+    <n v="73"/>
+    <s v="Dinesh"/>
     <x v="0"/>
-    <x v="22"/>
-    <x v="0"/>
-    <x v="0"/>
+    <s v="System Admin"/>
+    <x v="30"/>
+    <s v="Mumbai"/>
     <x v="44"/>
     <n v="5"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="73"/>
-    <x v="72"/>
+    <n v="74"/>
+    <s v="Shilpa"/>
     <x v="2"/>
-    <x v="7"/>
+    <s v="Analyst"/>
     <x v="33"/>
-    <x v="3"/>
+    <s v="Delhi"/>
     <x v="57"/>
     <n v="4"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="74"/>
-    <x v="73"/>
+    <n v="75"/>
+    <s v="Rajat"/>
     <x v="3"/>
-    <x v="8"/>
-    <x v="22"/>
-    <x v="1"/>
+    <s v="Manager"/>
+    <x v="21"/>
+    <s v="Pune"/>
     <x v="61"/>
     <n v="7"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="75"/>
-    <x v="74"/>
+    <n v="76"/>
+    <s v="Monika"/>
     <x v="1"/>
-    <x v="8"/>
+    <s v="Manager"/>
     <x v="40"/>
-    <x v="2"/>
+    <s v="Bangalore"/>
     <x v="54"/>
     <n v="7"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="76"/>
-    <x v="75"/>
+    <n v="77"/>
+    <s v="Arvind"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="25"/>
-    <x v="4"/>
+    <s v="Developer"/>
+    <x v="24"/>
+    <s v="Hyderabad"/>
     <x v="62"/>
     <n v="6"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="77"/>
-    <x v="76"/>
+    <n v="78"/>
+    <s v="Swati"/>
     <x v="2"/>
-    <x v="3"/>
-    <x v="24"/>
-    <x v="5"/>
+    <s v="Accountant"/>
+    <x v="23"/>
+    <s v="Chennai"/>
     <x v="63"/>
     <n v="3"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="78"/>
-    <x v="77"/>
+    <n v="79"/>
+    <s v="Lokesh"/>
     <x v="3"/>
-    <x v="11"/>
+    <s v="Executive"/>
     <x v="7"/>
-    <x v="0"/>
+    <s v="Mumbai"/>
     <x v="27"/>
     <n v="4"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="79"/>
-    <x v="78"/>
+    <n v="80"/>
+    <s v="Neetu"/>
     <x v="1"/>
-    <x v="1"/>
-    <x v="18"/>
-    <x v="3"/>
+    <s v="Recruiter"/>
+    <x v="17"/>
+    <s v="Delhi"/>
     <x v="64"/>
     <n v="3"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="80"/>
-    <x v="79"/>
+    <n v="81"/>
+    <s v="Varsha"/>
     <x v="0"/>
-    <x v="17"/>
+    <s v="Data Analyst"/>
     <x v="41"/>
-    <x v="1"/>
+    <s v="Pune"/>
     <x v="28"/>
     <n v="6"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="81"/>
-    <x v="80"/>
+    <n v="82"/>
+    <s v="Prakash"/>
     <x v="2"/>
-    <x v="8"/>
+    <s v="Manager"/>
     <x v="42"/>
-    <x v="2"/>
+    <s v="Bangalore"/>
     <x v="49"/>
     <n v="8"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="82"/>
-    <x v="81"/>
+    <n v="83"/>
+    <s v="Ritesh"/>
     <x v="3"/>
-    <x v="11"/>
-    <x v="28"/>
-    <x v="4"/>
+    <s v="Executive"/>
+    <x v="27"/>
+    <s v="Hyderabad"/>
     <x v="65"/>
     <n v="4"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="83"/>
-    <x v="82"/>
+    <n v="84"/>
+    <s v="Anu"/>
     <x v="1"/>
-    <x v="13"/>
-    <x v="23"/>
-    <x v="5"/>
+    <s v="Coordinator"/>
+    <x v="22"/>
+    <s v="Chennai"/>
     <x v="66"/>
     <n v="2"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="84"/>
-    <x v="83"/>
+    <n v="85"/>
+    <s v="Gopal"/>
     <x v="0"/>
-    <x v="15"/>
+    <s v="DevOps Engineer"/>
     <x v="43"/>
-    <x v="0"/>
+    <s v="Mumbai"/>
     <x v="67"/>
     <n v="7"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="85"/>
-    <x v="84"/>
+    <n v="86"/>
+    <s v="Suman"/>
     <x v="2"/>
-    <x v="7"/>
-    <x v="0"/>
-    <x v="3"/>
+    <s v="Analyst"/>
+    <x v="30"/>
+    <s v="Delhi"/>
     <x v="68"/>
     <n v="5"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="86"/>
-    <x v="85"/>
+    <n v="87"/>
+    <s v="Imran"/>
     <x v="3"/>
-    <x v="8"/>
-    <x v="14"/>
-    <x v="1"/>
+    <s v="Manager"/>
+    <x v="13"/>
+    <s v="Pune"/>
     <x v="61"/>
     <n v="7"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="87"/>
-    <x v="86"/>
+    <n v="88"/>
+    <s v="Kritika"/>
     <x v="1"/>
-    <x v="11"/>
+    <s v="Executive"/>
     <x v="1"/>
-    <x v="2"/>
+    <s v="Bangalore"/>
     <x v="40"/>
     <n v="3"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="88"/>
-    <x v="87"/>
+    <n v="89"/>
+    <s v="Ashok"/>
     <x v="0"/>
-    <x v="12"/>
+    <s v="Support Engineer"/>
     <x v="4"/>
-    <x v="4"/>
+    <s v="Hyderabad"/>
     <x v="34"/>
     <n v="3"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="89"/>
-    <x v="88"/>
+    <n v="90"/>
+    <s v="Reena"/>
     <x v="2"/>
-    <x v="3"/>
+    <s v="Accountant"/>
     <x v="12"/>
-    <x v="5"/>
+    <s v="Chennai"/>
     <x v="63"/>
     <n v="3"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="90"/>
-    <x v="89"/>
+    <n v="91"/>
+    <s v="Manoj"/>
     <x v="3"/>
-    <x v="11"/>
-    <x v="30"/>
-    <x v="0"/>
+    <s v="Executive"/>
+    <x v="29"/>
+    <s v="Mumbai"/>
     <x v="27"/>
     <n v="4"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="91"/>
-    <x v="90"/>
+    <n v="92"/>
+    <s v="Ruchi"/>
     <x v="1"/>
-    <x v="8"/>
+    <s v="Manager"/>
     <x v="44"/>
-    <x v="3"/>
+    <s v="Delhi"/>
     <x v="42"/>
     <n v="7"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="92"/>
-    <x v="91"/>
+    <n v="93"/>
+    <s v="Dev"/>
     <x v="0"/>
-    <x v="0"/>
-    <x v="29"/>
-    <x v="1"/>
+    <s v="Developer"/>
+    <x v="28"/>
+    <s v="Pune"/>
     <x v="28"/>
     <n v="6"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="93"/>
-    <x v="92"/>
+    <n v="94"/>
+    <s v="Kajal"/>
     <x v="2"/>
-    <x v="7"/>
+    <s v="Analyst"/>
     <x v="33"/>
-    <x v="2"/>
+    <s v="Bangalore"/>
     <x v="17"/>
     <n v="5"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="94"/>
-    <x v="93"/>
+    <n v="95"/>
+    <s v="Siddharth"/>
     <x v="3"/>
-    <x v="8"/>
+    <s v="Manager"/>
     <x v="45"/>
-    <x v="4"/>
+    <s v="Hyderabad"/>
     <x v="69"/>
     <n v="8"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="95"/>
-    <x v="94"/>
+    <n v="96"/>
+    <s v="Priti"/>
     <x v="1"/>
-    <x v="1"/>
-    <x v="18"/>
-    <x v="5"/>
+    <s v="Recruiter"/>
+    <x v="17"/>
+    <s v="Chennai"/>
     <x v="60"/>
     <n v="3"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="96"/>
-    <x v="44"/>
+    <n v="97"/>
+    <s v="Naveen"/>
     <x v="0"/>
-    <x v="18"/>
+    <s v="Data Scientist"/>
     <x v="46"/>
-    <x v="0"/>
+    <s v="Mumbai"/>
     <x v="70"/>
     <n v="7"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="97"/>
-    <x v="95"/>
+    <n v="98"/>
+    <s v="Geeta"/>
     <x v="2"/>
-    <x v="8"/>
+    <s v="Manager"/>
     <x v="47"/>
-    <x v="3"/>
+    <s v="Delhi"/>
     <x v="71"/>
     <n v="8"/>
     <x v="1"/>
   </r>
   <r>
-    <x v="98"/>
-    <x v="96"/>
+    <n v="99"/>
+    <s v="Akshay"/>
     <x v="3"/>
-    <x v="11"/>
-    <x v="21"/>
-    <x v="1"/>
+    <s v="Executive"/>
+    <x v="20"/>
+    <s v="Pune"/>
     <x v="72"/>
     <n v="4"/>
     <x v="0"/>
   </r>
   <r>
-    <x v="99"/>
-    <x v="47"/>
+    <n v="100"/>
+    <s v="Sonal"/>
     <x v="1"/>
-    <x v="13"/>
+    <s v="Coordinator"/>
     <x v="11"/>
-    <x v="2"/>
+    <s v="Bangalore"/>
     <x v="73"/>
     <n v="2"/>
     <x v="1"/>
@@ -5842,7 +6377,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0EFA4B00-DF2C-404C-B1D8-3FAEE0685836}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{0EFA4B00-DF2C-404C-B1D8-3FAEE0685836}" name="PivotTable3" cacheId="91" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="I9:J12" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField dataField="1" showAll="0"/>
@@ -5859,29 +6394,29 @@
     <pivotField showAll="0"/>
     <pivotField showAll="0">
       <items count="49">
-        <item x="15"/>
+        <item x="14"/>
         <item x="11"/>
-        <item x="23"/>
+        <item x="22"/>
         <item x="1"/>
-        <item x="18"/>
+        <item x="17"/>
         <item x="37"/>
         <item x="9"/>
-        <item x="17"/>
+        <item x="16"/>
         <item x="12"/>
         <item x="3"/>
+        <item x="23"/>
+        <item x="4"/>
+        <item x="29"/>
+        <item x="7"/>
+        <item x="27"/>
+        <item x="20"/>
+        <item x="30"/>
+        <item x="33"/>
+        <item x="26"/>
+        <item x="18"/>
+        <item x="0"/>
         <item x="24"/>
-        <item x="4"/>
-        <item x="30"/>
-        <item x="7"/>
         <item x="28"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="33"/>
-        <item x="27"/>
-        <item x="19"/>
-        <item x="13"/>
-        <item x="25"/>
-        <item x="29"/>
         <item x="34"/>
         <item x="36"/>
         <item x="5"/>
@@ -5889,24 +6424,24 @@
         <item x="10"/>
         <item x="8"/>
         <item x="35"/>
-        <item x="20"/>
+        <item x="19"/>
         <item x="40"/>
         <item x="44"/>
         <item x="2"/>
         <item x="39"/>
         <item x="31"/>
-        <item x="22"/>
+        <item x="21"/>
         <item x="43"/>
-        <item x="14"/>
+        <item x="13"/>
         <item x="45"/>
-        <item x="26"/>
+        <item x="25"/>
         <item x="38"/>
         <item x="32"/>
         <item x="42"/>
         <item x="47"/>
         <item x="6"/>
         <item x="46"/>
-        <item x="16"/>
+        <item x="15"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -6064,16 +6599,16 @@
     <dataField name="Count of EMP_ID" fld="0" subtotal="count" baseField="8" baseItem="0"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="3">
+    <format dxfId="258">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="2">
+    <format dxfId="257">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="1">
+    <format dxfId="256">
       <pivotArea field="8" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="0">
+    <format dxfId="255">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -6125,7 +6660,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D5C2D675-5A19-4203-B90D-4469467E5F28}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D5C2D675-5A19-4203-B90D-4469467E5F28}" name="PivotTable2" cacheId="91" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="F9:G14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
     <pivotField showAll="0"/>
@@ -6142,29 +6677,29 @@
     <pivotField showAll="0"/>
     <pivotField dataField="1" showAll="0">
       <items count="49">
-        <item x="15"/>
+        <item x="14"/>
         <item x="11"/>
-        <item x="23"/>
+        <item x="22"/>
         <item x="1"/>
-        <item x="18"/>
+        <item x="17"/>
         <item x="37"/>
         <item x="9"/>
-        <item x="17"/>
+        <item x="16"/>
         <item x="12"/>
         <item x="3"/>
+        <item x="23"/>
+        <item x="4"/>
+        <item x="29"/>
+        <item x="7"/>
+        <item x="27"/>
+        <item x="20"/>
+        <item x="30"/>
+        <item x="33"/>
+        <item x="26"/>
+        <item x="18"/>
+        <item x="0"/>
         <item x="24"/>
-        <item x="4"/>
-        <item x="30"/>
-        <item x="7"/>
         <item x="28"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="33"/>
-        <item x="27"/>
-        <item x="19"/>
-        <item x="13"/>
-        <item x="25"/>
-        <item x="29"/>
         <item x="34"/>
         <item x="36"/>
         <item x="5"/>
@@ -6172,24 +6707,24 @@
         <item x="10"/>
         <item x="8"/>
         <item x="35"/>
-        <item x="20"/>
+        <item x="19"/>
         <item x="40"/>
         <item x="44"/>
         <item x="2"/>
         <item x="39"/>
         <item x="31"/>
-        <item x="22"/>
+        <item x="21"/>
         <item x="43"/>
-        <item x="14"/>
+        <item x="13"/>
         <item x="45"/>
-        <item x="26"/>
+        <item x="25"/>
         <item x="38"/>
         <item x="32"/>
         <item x="42"/>
         <item x="47"/>
         <item x="6"/>
         <item x="46"/>
-        <item x="16"/>
+        <item x="15"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -6347,7 +6882,7 @@
     <dataField name="Sum of SALARY" fld="4" baseField="0" baseItem="0"/>
   </dataFields>
   <formats count="9">
-    <format dxfId="12">
+    <format dxfId="267">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -6356,7 +6891,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="11">
+    <format dxfId="266">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -6365,7 +6900,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="10">
+    <format dxfId="265">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -6374,7 +6909,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="9">
+    <format dxfId="264">
       <pivotArea collapsedLevelsAreSubtotals="1" fieldPosition="0">
         <references count="1">
           <reference field="2" count="1">
@@ -6383,19 +6918,19 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="8">
+    <format dxfId="263">
       <pivotArea grandRow="1" outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="7">
+    <format dxfId="262">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="6">
+    <format dxfId="261">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="5">
+    <format dxfId="260">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="4">
+    <format dxfId="259">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -6423,216 +6958,11 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4C3C0FDF-7392-4307-A3FB-135F9497C134}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{4C3C0FDF-7392-4307-A3FB-135F9497C134}" name="PivotTable1" cacheId="91" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="10">
   <location ref="C9:D14" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="12">
-    <pivotField dataField="1" showAll="0">
-      <items count="101">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item x="3"/>
-        <item x="4"/>
-        <item x="5"/>
-        <item x="6"/>
-        <item x="7"/>
-        <item x="8"/>
-        <item x="9"/>
-        <item x="10"/>
-        <item x="11"/>
-        <item x="12"/>
-        <item x="13"/>
-        <item x="14"/>
-        <item x="15"/>
-        <item x="16"/>
-        <item x="17"/>
-        <item x="18"/>
-        <item x="19"/>
-        <item x="20"/>
-        <item x="21"/>
-        <item x="22"/>
-        <item x="23"/>
-        <item x="24"/>
-        <item x="25"/>
-        <item x="26"/>
-        <item x="27"/>
-        <item x="28"/>
-        <item x="29"/>
-        <item x="30"/>
-        <item x="31"/>
-        <item x="32"/>
-        <item x="33"/>
-        <item x="34"/>
-        <item x="35"/>
-        <item x="36"/>
-        <item x="37"/>
-        <item x="38"/>
-        <item x="39"/>
-        <item x="40"/>
-        <item x="41"/>
-        <item x="42"/>
-        <item x="43"/>
-        <item x="44"/>
-        <item x="45"/>
-        <item x="46"/>
-        <item x="47"/>
-        <item x="48"/>
-        <item x="49"/>
-        <item x="50"/>
-        <item x="51"/>
-        <item x="52"/>
-        <item x="53"/>
-        <item x="54"/>
-        <item x="55"/>
-        <item x="56"/>
-        <item x="57"/>
-        <item x="58"/>
-        <item x="59"/>
-        <item x="60"/>
-        <item x="61"/>
-        <item x="62"/>
-        <item x="63"/>
-        <item x="64"/>
-        <item x="65"/>
-        <item x="66"/>
-        <item x="67"/>
-        <item x="68"/>
-        <item x="69"/>
-        <item x="70"/>
-        <item x="71"/>
-        <item x="72"/>
-        <item x="73"/>
-        <item x="74"/>
-        <item x="75"/>
-        <item x="76"/>
-        <item x="77"/>
-        <item x="78"/>
-        <item x="79"/>
-        <item x="80"/>
-        <item x="81"/>
-        <item x="82"/>
-        <item x="83"/>
-        <item x="84"/>
-        <item x="85"/>
-        <item x="86"/>
-        <item x="87"/>
-        <item x="88"/>
-        <item x="89"/>
-        <item x="90"/>
-        <item x="91"/>
-        <item x="92"/>
-        <item x="93"/>
-        <item x="94"/>
-        <item x="95"/>
-        <item x="96"/>
-        <item x="97"/>
-        <item x="98"/>
-        <item x="99"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="98">
-        <item sd="0" x="67"/>
-        <item sd="0" x="48"/>
-        <item sd="0" x="28"/>
-        <item sd="0" x="96"/>
-        <item sd="0" x="56"/>
-        <item sd="0" x="22"/>
-        <item x="60"/>
-        <item x="2"/>
-        <item x="13"/>
-        <item x="58"/>
-        <item x="82"/>
-        <item x="6"/>
-        <item x="75"/>
-        <item x="87"/>
-        <item x="30"/>
-        <item x="68"/>
-        <item x="49"/>
-        <item x="14"/>
-        <item x="91"/>
-        <item x="71"/>
-        <item x="29"/>
-        <item x="26"/>
-        <item x="95"/>
-        <item x="57"/>
-        <item x="83"/>
-        <item x="34"/>
-        <item x="85"/>
-        <item x="43"/>
-        <item x="70"/>
-        <item x="92"/>
-        <item x="69"/>
-        <item x="10"/>
-        <item x="7"/>
-        <item x="63"/>
-        <item x="35"/>
-        <item x="16"/>
-        <item x="86"/>
-        <item x="52"/>
-        <item x="77"/>
-        <item x="21"/>
-        <item x="89"/>
-        <item x="11"/>
-        <item x="53"/>
-        <item x="42"/>
-        <item x="74"/>
-        <item x="44"/>
-        <item x="36"/>
-        <item x="78"/>
-        <item x="5"/>
-        <item x="54"/>
-        <item x="65"/>
-        <item x="25"/>
-        <item x="17"/>
-        <item x="33"/>
-        <item x="40"/>
-        <item x="27"/>
-        <item x="9"/>
-        <item x="80"/>
-        <item x="59"/>
-        <item x="94"/>
-        <item x="3"/>
-        <item x="61"/>
-        <item x="0"/>
-        <item x="73"/>
-        <item x="15"/>
-        <item x="31"/>
-        <item x="88"/>
-        <item x="41"/>
-        <item x="81"/>
-        <item x="20"/>
-        <item x="45"/>
-        <item x="50"/>
-        <item x="4"/>
-        <item x="90"/>
-        <item x="39"/>
-        <item x="64"/>
-        <item x="55"/>
-        <item x="18"/>
-        <item x="72"/>
-        <item x="23"/>
-        <item x="93"/>
-        <item x="51"/>
-        <item x="1"/>
-        <item x="47"/>
-        <item x="84"/>
-        <item x="32"/>
-        <item x="8"/>
-        <item x="76"/>
-        <item x="38"/>
-        <item x="24"/>
-        <item x="66"/>
-        <item x="79"/>
-        <item x="19"/>
-        <item x="12"/>
-        <item x="46"/>
-        <item x="62"/>
-        <item x="37"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
     <pivotField axis="axisRow" showAll="0">
       <items count="5">
         <item x="2"/>
@@ -6642,59 +6972,32 @@
         <item t="default"/>
       </items>
     </pivotField>
+    <pivotField showAll="0"/>
     <pivotField showAll="0">
-      <items count="24">
+      <items count="49">
+        <item x="14"/>
+        <item x="11"/>
+        <item x="22"/>
+        <item x="1"/>
+        <item x="17"/>
+        <item x="37"/>
+        <item x="9"/>
+        <item x="16"/>
+        <item x="12"/>
         <item x="3"/>
+        <item x="23"/>
+        <item x="4"/>
+        <item x="29"/>
         <item x="7"/>
-        <item x="14"/>
-        <item sd="0" x="19"/>
-        <item x="13"/>
-        <item x="17"/>
-        <item sd="0" x="21"/>
+        <item x="27"/>
+        <item x="20"/>
+        <item x="30"/>
+        <item x="33"/>
+        <item x="26"/>
         <item x="18"/>
         <item x="0"/>
-        <item x="15"/>
-        <item x="11"/>
-        <item x="20"/>
-        <item x="16"/>
-        <item x="5"/>
-        <item x="8"/>
-        <item x="1"/>
-        <item x="4"/>
-        <item x="10"/>
-        <item x="2"/>
-        <item x="12"/>
-        <item x="22"/>
-        <item x="6"/>
-        <item x="9"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0">
-      <items count="49">
-        <item x="15"/>
-        <item x="11"/>
-        <item x="23"/>
-        <item x="1"/>
-        <item x="18"/>
-        <item x="37"/>
-        <item x="9"/>
-        <item x="17"/>
-        <item x="12"/>
-        <item x="3"/>
         <item x="24"/>
-        <item x="4"/>
-        <item x="30"/>
-        <item x="7"/>
         <item x="28"/>
-        <item x="21"/>
-        <item x="0"/>
-        <item x="33"/>
-        <item x="27"/>
-        <item x="19"/>
-        <item x="13"/>
-        <item x="25"/>
-        <item x="29"/>
         <item x="34"/>
         <item x="36"/>
         <item x="5"/>
@@ -6702,24 +7005,24 @@
         <item x="10"/>
         <item x="8"/>
         <item x="35"/>
-        <item x="20"/>
+        <item x="19"/>
         <item x="40"/>
         <item x="44"/>
         <item x="2"/>
         <item x="39"/>
         <item x="31"/>
-        <item x="22"/>
+        <item x="21"/>
         <item x="43"/>
-        <item x="14"/>
+        <item x="13"/>
         <item x="45"/>
-        <item x="26"/>
+        <item x="25"/>
         <item x="38"/>
         <item x="32"/>
         <item x="42"/>
         <item x="47"/>
         <item x="6"/>
         <item x="46"/>
-        <item x="16"/>
+        <item x="15"/>
         <item t="default"/>
       </items>
     </pivotField>
@@ -6877,16 +7180,16 @@
     <dataField name="Count of EMP_ID" fld="0" subtotal="count" baseField="2" baseItem="0"/>
   </dataFields>
   <formats count="4">
-    <format dxfId="16">
+    <format dxfId="271">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
-    <format dxfId="15">
+    <format dxfId="270">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="14">
+    <format dxfId="269">
       <pivotArea field="2" type="button" dataOnly="0" labelOnly="1" outline="0" axis="axisRow" fieldPosition="0"/>
     </format>
-    <format dxfId="13">
+    <format dxfId="268">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" axis="axisValues" fieldPosition="0"/>
     </format>
   </formats>
@@ -6943,29 +7246,29 @@
   <data>
     <tabular pivotCacheId="1404190004">
       <items count="48">
-        <i x="15" s="1"/>
+        <i x="14" s="1"/>
         <i x="11" s="1"/>
-        <i x="23" s="1"/>
+        <i x="22" s="1"/>
         <i x="1" s="1"/>
-        <i x="18" s="1"/>
+        <i x="17" s="1"/>
         <i x="37" s="1"/>
         <i x="9" s="1"/>
-        <i x="17" s="1"/>
+        <i x="16" s="1"/>
         <i x="12" s="1"/>
         <i x="3" s="1"/>
+        <i x="23" s="1"/>
+        <i x="4" s="1"/>
+        <i x="29" s="1"/>
+        <i x="7" s="1"/>
+        <i x="27" s="1"/>
+        <i x="20" s="1"/>
+        <i x="30" s="1"/>
+        <i x="33" s="1"/>
+        <i x="26" s="1"/>
+        <i x="18" s="1"/>
+        <i x="0" s="1"/>
         <i x="24" s="1"/>
-        <i x="4" s="1"/>
-        <i x="30" s="1"/>
-        <i x="7" s="1"/>
         <i x="28" s="1"/>
-        <i x="21" s="1"/>
-        <i x="0" s="1"/>
-        <i x="33" s="1"/>
-        <i x="27" s="1"/>
-        <i x="19" s="1"/>
-        <i x="13" s="1"/>
-        <i x="25" s="1"/>
-        <i x="29" s="1"/>
         <i x="34" s="1"/>
         <i x="36" s="1"/>
         <i x="5" s="1"/>
@@ -6973,24 +7276,24 @@
         <i x="10" s="1"/>
         <i x="8" s="1"/>
         <i x="35" s="1"/>
-        <i x="20" s="1"/>
+        <i x="19" s="1"/>
         <i x="40" s="1"/>
         <i x="44" s="1"/>
         <i x="2" s="1"/>
         <i x="39" s="1"/>
         <i x="31" s="1"/>
-        <i x="22" s="1"/>
+        <i x="21" s="1"/>
         <i x="43" s="1"/>
-        <i x="14" s="1"/>
+        <i x="13" s="1"/>
         <i x="45" s="1"/>
-        <i x="26" s="1"/>
+        <i x="25" s="1"/>
         <i x="38" s="1"/>
         <i x="32" s="1"/>
         <i x="42" s="1"/>
         <i x="47" s="1"/>
         <i x="6" s="1"/>
         <i x="46" s="1"/>
-        <i x="16" s="1"/>
+        <i x="15" s="1"/>
       </items>
     </tabular>
   </data>
@@ -7374,13 +7677,10 @@
       <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="21"/>
-      <c r="M1" s="22"/>
-      <c r="N1" s="21"/>
-      <c r="O1" s="22"/>
-      <c r="P1" s="21"/>
-      <c r="Q1" s="22"/>
-      <c r="R1" s="21"/>
+      <c r="L1" s="16"/>
+      <c r="N1" s="16"/>
+      <c r="P1" s="16"/>
+      <c r="R1" s="16"/>
     </row>
     <row r="2" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
@@ -7396,7 +7696,7 @@
         <v>11</v>
       </c>
       <c r="E2" s="2">
-        <v>55000</v>
+        <v>60000</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>12</v>
@@ -7410,13 +7710,10 @@
       <c r="I2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="L2" s="23"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="24"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="24"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="24"/>
+      <c r="L2" s="17"/>
+      <c r="N2" s="18"/>
+      <c r="P2" s="18"/>
+      <c r="R2" s="18"/>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
@@ -10306,54 +10603,54 @@
   <cols>
     <col min="1" max="1" width="1.77734375" customWidth="1"/>
     <col min="2" max="2" width="4.44140625" customWidth="1"/>
-    <col min="3" max="3" width="20.77734375" customWidth="1"/>
-    <col min="4" max="4" width="15.109375" customWidth="1"/>
+    <col min="3" max="3" width="15.77734375" customWidth="1"/>
+    <col min="4" max="4" width="17.88671875" customWidth="1"/>
     <col min="5" max="5" width="25.44140625" customWidth="1"/>
     <col min="6" max="6" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.21875" customWidth="1"/>
-    <col min="8" max="8" width="17.109375" customWidth="1"/>
-    <col min="9" max="9" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18.44140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
+      <c r="I1" s="26"/>
+      <c r="J1" s="26"/>
     </row>
     <row r="2" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="26"/>
+      <c r="D2" s="26"/>
+      <c r="E2" s="26"/>
+      <c r="F2" s="26"/>
+      <c r="G2" s="26"/>
+      <c r="H2" s="26"/>
+      <c r="I2" s="26"/>
+      <c r="J2" s="26"/>
     </row>
     <row r="4" spans="1:10" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="20" t="s">
+      <c r="C4" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="E4" s="20" t="s">
+      <c r="E4" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="I4" s="20" t="s">
+      <c r="I4" s="15" t="s">
         <v>174</v>
       </c>
     </row>
@@ -10364,7 +10661,7 @@
       </c>
       <c r="E5" s="8">
         <f>AVERAGE('HR DATA'!E2:E101)</f>
-        <v>59210</v>
+        <v>59260</v>
       </c>
       <c r="G5" s="8">
         <f>MAX('HR DATA'!E2:E101)</f>
@@ -10376,18 +10673,18 @@
       </c>
     </row>
     <row r="7" spans="1:10" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="28" t="s">
         <v>148</v>
       </c>
-      <c r="D7" s="15"/>
-      <c r="F7" s="15" t="s">
+      <c r="D7" s="28"/>
+      <c r="F7" s="28" t="s">
         <v>149</v>
       </c>
-      <c r="G7" s="15"/>
-      <c r="I7" s="15" t="s">
+      <c r="G7" s="28"/>
+      <c r="I7" s="28" t="s">
         <v>150</v>
       </c>
-      <c r="J7" s="15"/>
+      <c r="J7" s="28"/>
     </row>
     <row r="8" spans="1:10" ht="5.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="9" spans="1:10" ht="19.8" customHeight="1" x14ac:dyDescent="0.3">
@@ -10414,7 +10711,7 @@
       <c r="C10" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="27">
         <v>24</v>
       </c>
       <c r="F10" s="6" t="s">
@@ -10426,7 +10723,7 @@
       <c r="I10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="27">
         <v>47</v>
       </c>
     </row>
@@ -10434,7 +10731,7 @@
       <c r="C11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="27">
         <v>24</v>
       </c>
       <c r="F11" s="6" t="s">
@@ -10446,7 +10743,7 @@
       <c r="I11" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="27">
         <v>53</v>
       </c>
     </row>
@@ -10454,19 +10751,19 @@
       <c r="C12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="27">
         <v>29</v>
       </c>
       <c r="F12" s="6" t="s">
         <v>10</v>
       </c>
       <c r="G12" s="9">
-        <v>1909000</v>
+        <v>1914000</v>
       </c>
       <c r="I12" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="27">
         <v>100</v>
       </c>
     </row>
@@ -10474,7 +10771,7 @@
       <c r="C13" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="27">
         <v>23</v>
       </c>
       <c r="F13" s="6" t="s">
@@ -10488,14 +10785,14 @@
       <c r="C14" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="27">
         <v>100</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>145</v>
       </c>
       <c r="G14" s="9">
-        <v>5921000</v>
+        <v>5926000</v>
       </c>
     </row>
     <row r="23" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -10533,28 +10830,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="B1" s="28"/>
+      <c r="B1" s="25"/>
     </row>
     <row r="2" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B2" s="26" t="s">
+      <c r="B2" s="20" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
+      <c r="A3" s="21"/>
       <c r="B3" s="7" t="s">
         <v>151</v>
       </c>
       <c r="H3" s="1"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="19"/>
+      <c r="A4" s="23"/>
       <c r="B4" s="7"/>
       <c r="H4" s="1"/>
     </row>
@@ -10562,34 +10859,34 @@
       <c r="A5" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="20" t="s">
         <v>164</v>
       </c>
       <c r="H5" s="1"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="17"/>
+      <c r="A6" s="21"/>
       <c r="B6" s="7" t="s">
         <v>153</v>
       </c>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="18"/>
+      <c r="A7" s="22"/>
       <c r="B7" s="7" t="s">
         <v>154</v>
       </c>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="18"/>
+      <c r="A8" s="22"/>
       <c r="B8" s="7" t="s">
         <v>152</v>
       </c>
       <c r="H8" s="1"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="19"/>
+      <c r="A9" s="23"/>
       <c r="B9" s="7"/>
       <c r="H9" s="1"/>
     </row>
@@ -10597,34 +10894,34 @@
       <c r="A10" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="20" t="s">
         <v>165</v>
       </c>
       <c r="H10" s="1"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="17"/>
+      <c r="A11" s="21"/>
       <c r="B11" s="7" t="s">
         <v>155</v>
       </c>
       <c r="H11" s="1"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="18"/>
+      <c r="A12" s="22"/>
       <c r="B12" s="7" t="s">
         <v>156</v>
       </c>
       <c r="H12" s="1"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="18"/>
+      <c r="A13" s="22"/>
       <c r="B13" s="7" t="s">
         <v>157</v>
       </c>
       <c r="H13" s="1"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="19"/>
+      <c r="A14" s="23"/>
       <c r="B14" s="7"/>
       <c r="H14" s="1"/>
     </row>
@@ -10632,35 +10929,35 @@
       <c r="A15" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="B15" s="26" t="s">
+      <c r="B15" s="20" t="s">
         <v>166</v>
       </c>
       <c r="H15" s="1"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="17"/>
+      <c r="A16" s="21"/>
       <c r="B16" s="7" t="s">
         <v>158</v>
       </c>
       <c r="H16" s="1"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="18"/>
+      <c r="A17" s="22"/>
       <c r="B17" s="7" t="s">
         <v>159</v>
       </c>
       <c r="H17" s="1"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="19"/>
+      <c r="A18" s="23"/>
       <c r="B18" s="7"/>
       <c r="H18" s="1"/>
     </row>
     <row r="19" spans="1:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="25" t="s">
+      <c r="A19" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="B19" s="26" t="s">
+      <c r="B19" s="20" t="s">
         <v>177</v>
       </c>
       <c r="H19" s="1"/>
@@ -10673,7 +10970,7 @@
       <c r="H20" s="1"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="25"/>
+      <c r="A21" s="19"/>
       <c r="B21" s="7"/>
       <c r="H21" s="1"/>
     </row>
@@ -10681,27 +10978,27 @@
       <c r="A22" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="B22" s="20" t="s">
         <v>162</v>
       </c>
       <c r="H22" s="1"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="17"/>
+      <c r="A23" s="21"/>
       <c r="B23" t="s">
         <v>175</v>
       </c>
       <c r="H23" s="1"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="18"/>
+      <c r="A24" s="22"/>
       <c r="B24" s="7" t="s">
         <v>160</v>
       </c>
       <c r="H24" s="1"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="19"/>
+      <c r="A25" s="23"/>
       <c r="B25" s="7" t="s">
         <v>161</v>
       </c>
